--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.42848751862366</v>
+        <v>2.019629221776345</v>
       </c>
       <c r="D2" t="n">
-        <v>9.487222151682234</v>
+        <v>1.541673599648363</v>
       </c>
       <c r="E2" t="n">
-        <v>8.681474287967694</v>
+        <v>1.41073957179475</v>
       </c>
       <c r="F2" t="n">
-        <v>8.835774828925549</v>
+        <v>1.435813409700401</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.69776020423538</v>
+        <v>3.36338603318825</v>
       </c>
       <c r="D3" t="n">
-        <v>20.69776020423538</v>
+        <v>3.36338603318825</v>
       </c>
       <c r="E3" t="n">
-        <v>8.681474287967694</v>
+        <v>1.41073957179475</v>
       </c>
       <c r="F3" t="n">
-        <v>8.835774828925549</v>
+        <v>1.435813409700401</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.69690670094801</v>
+        <v>3.688247338904052</v>
       </c>
       <c r="D4" t="n">
-        <v>22.02810465534554</v>
+        <v>3.579567006493651</v>
       </c>
       <c r="E4" t="n">
-        <v>8.681474287967694</v>
+        <v>1.41073957179475</v>
       </c>
       <c r="F4" t="n">
-        <v>8.835774828925549</v>
+        <v>1.435813409700401</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.348025055905979</v>
+        <v>1.194054071584722</v>
       </c>
       <c r="D5" t="n">
-        <v>7.901141637784851</v>
+        <v>1.283935516140038</v>
       </c>
       <c r="E5" t="n">
-        <v>8.681474287967694</v>
+        <v>1.41073957179475</v>
       </c>
       <c r="F5" t="n">
-        <v>8.835774828925549</v>
+        <v>1.435813409700401</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.77419610322055</v>
+        <v>4.83830686677334</v>
       </c>
       <c r="D6" t="n">
-        <v>29.74408944434367</v>
+        <v>4.833414534705846</v>
       </c>
       <c r="E6" t="n">
-        <v>8.681474287967694</v>
+        <v>1.41073957179475</v>
       </c>
       <c r="F6" t="n">
-        <v>8.835774828925549</v>
+        <v>1.435813409700401</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.559900273321763</v>
+        <v>0.9034837944147865</v>
       </c>
       <c r="D7" t="n">
-        <v>5.359858925054112</v>
+        <v>0.8709770753212933</v>
       </c>
       <c r="E7" t="n">
-        <v>8.681474287967694</v>
+        <v>1.41073957179475</v>
       </c>
       <c r="F7" t="n">
-        <v>8.835774828925549</v>
+        <v>1.435813409700401</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
